--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B3_2026.xlsx
@@ -2832,7 +2832,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>31/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="B6" t="str">
         <v>Jul26</v>
@@ -2844,10 +2844,10 @@
         <v>Rental</v>
       </c>
       <c r="E6" t="str">
-        <v>Rent B3</v>
+        <v>ค่าเช่า Platinum Pop ก.ค. (สัญญา MWA01 ช่วง 10-31 ก.ค.) [bank 10/07]</v>
       </c>
       <c r="F6">
-        <v>19000</v>
+        <v>13146.16</v>
       </c>
     </row>
     <row r="7">
